--- a/Den tat/data/Danhsachdentat.xlsx
+++ b/Den tat/data/Danhsachdentat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maivu\Documents\GitHub\cskvtt\Den tat\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB4F8A9-91E8-466E-82FD-84C24B59A723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C482B0-B185-4B24-AF12-3E57E9D1CB2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{A1266DFF-32F5-4B0B-A729-2A44814C55C6}"/>
   </bookViews>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>latitude</t>
   </si>
@@ -195,6 +195,12 @@
   </si>
   <si>
     <t>HÌnh ảnh</t>
+  </si>
+  <si>
+    <t>Người phát hiện</t>
+  </si>
+  <si>
+    <t>Người sửa</t>
   </si>
 </sst>
 </file>
@@ -930,7 +936,43 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="19">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1236,26 +1278,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{57F7D91B-22BC-49D0-B4E3-985709940F43}" name="Table1" displayName="Table1" ref="A1:Q2" insertRow="1" totalsRowShown="0" headerRowDxfId="16" tableBorderDxfId="15">
-  <autoFilter ref="A1:Q2" xr:uid="{57F7D91B-22BC-49D0-B4E3-985709940F43}"/>
-  <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{C6718836-1ADA-436E-8248-FEF66CCE4679}" name="ID" dataDxfId="14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{57F7D91B-22BC-49D0-B4E3-985709940F43}" name="Table1" displayName="Table1" ref="A1:S2" insertRow="1" totalsRowShown="0" headerRowDxfId="18" tableBorderDxfId="17">
+  <autoFilter ref="A1:S2" xr:uid="{57F7D91B-22BC-49D0-B4E3-985709940F43}"/>
+  <tableColumns count="19">
+    <tableColumn id="1" xr3:uid="{C6718836-1ADA-436E-8248-FEF66CCE4679}" name="ID" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{50D8814C-95FB-4254-AC87-8B23CB11EAF5}" name="Số trụ"/>
-    <tableColumn id="15" xr3:uid="{CB056CA1-8680-427B-B2EC-E92EE111CB4C}" name="Tên tủ" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{62737F73-6B22-452A-AA5E-4D77D788AA2D}" name="latitude" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{F21613BC-6878-4C9F-98A8-BC3B7671840C}" name="lontitude" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{510B7215-A02C-4542-8653-A22DB7A9E34A}" name="Loại đèn" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{98930E79-6C50-4716-9779-BFEB7232C21A}" name="Công suất" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{5B88161E-6793-4B8B-953A-E29DF281AC2A}" name="Trang thai" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{CB056CA1-8680-427B-B2EC-E92EE111CB4C}" name="Tên tủ" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{62737F73-6B22-452A-AA5E-4D77D788AA2D}" name="latitude" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{F21613BC-6878-4C9F-98A8-BC3B7671840C}" name="lontitude" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{510B7215-A02C-4542-8653-A22DB7A9E34A}" name="Loại đèn" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{98930E79-6C50-4716-9779-BFEB7232C21A}" name="Công suất" dataDxfId="11"/>
+    <tableColumn id="7" xr3:uid="{5B88161E-6793-4B8B-953A-E29DF281AC2A}" name="Trang thai" dataDxfId="10"/>
     <tableColumn id="12" xr3:uid="{D23D0C74-146D-4AE1-8936-E72E3FA5E682}" name="Đường"/>
-    <tableColumn id="13" xr3:uid="{2E5CBD41-DDA4-4783-9CDE-2F945C2B6CA4}" name="Phường" dataDxfId="7"/>
-    <tableColumn id="17" xr3:uid="{84EBDEC4-E78C-4AA4-B311-861099BF6B65}" name="Ngày phát hiện" dataDxfId="6"/>
-    <tableColumn id="18" xr3:uid="{CB92BEE5-88D5-4F3C-920C-247E81EE36AA}" name="Ngày sửa" dataDxfId="5"/>
-    <tableColumn id="19" xr3:uid="{B40E1775-B2AF-4675-8FF2-ECC65BE981AB}" name="Vật tư sửa" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{0BF4558C-2FDD-4E16-B7DD-05EC975BBF58}" name="HÌnh ảnh" dataDxfId="0"/>
-    <tableColumn id="16" xr3:uid="{D0331976-FF70-4630-A43E-42F7FE297363}" name="Ghi chú" dataDxfId="3"/>
-    <tableColumn id="20" xr3:uid="{CEF5FB37-78DD-4788-97C0-CFFDA9C56144}" name="VN2000-X" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{98A1D069-86A0-4943-9D17-A6212B4D7D40}" name="VN2000-Y" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{2E5CBD41-DDA4-4783-9CDE-2F945C2B6CA4}" name="Phường" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{84EBDEC4-E78C-4AA4-B311-861099BF6B65}" name="Ngày phát hiện" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{3A698E63-5F86-4B4A-8C77-2BE49A02BF25}" name="Người phát hiện" dataDxfId="1"/>
+    <tableColumn id="18" xr3:uid="{CB92BEE5-88D5-4F3C-920C-247E81EE36AA}" name="Ngày sửa" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{86FBDEB3-69FC-4F63-AF07-1335F6B7A9E6}" name="Người sửa" dataDxfId="0"/>
+    <tableColumn id="19" xr3:uid="{B40E1775-B2AF-4675-8FF2-ECC65BE981AB}" name="Vật tư sửa" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{0BF4558C-2FDD-4E16-B7DD-05EC975BBF58}" name="HÌnh ảnh" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{D0331976-FF70-4630-A43E-42F7FE297363}" name="Ghi chú" dataDxfId="4"/>
+    <tableColumn id="20" xr3:uid="{CEF5FB37-78DD-4788-97C0-CFFDA9C56144}" name="VN2000-X" dataDxfId="3"/>
+    <tableColumn id="21" xr3:uid="{98A1D069-86A0-4943-9D17-A6212B4D7D40}" name="VN2000-Y" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1579,7 +1623,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86673E56-9A8C-4B3E-BC42-A6E3991962E7}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -1592,16 +1636,16 @@
     <col min="8" max="8" width="12" style="12" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="15.42578125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="15.42578125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="15.42578125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.28515625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="15.42578125" style="1" customWidth="1"/>
     <col min="18" max="18" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
@@ -1636,25 +1680,31 @@
         <v>23</v>
       </c>
       <c r="L1" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="N1" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="P1" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="Q1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1667,10 +1717,12 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D3"/>
       <c r="H3"/>
       <c r="J3"/>
@@ -1679,6 +1731,8 @@
       <c r="M3"/>
       <c r="N3"/>
       <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>
